--- a/Speciallægeloft/speciallægeloft_data/Steno.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Steno.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
   <si>
     <t xml:space="preserve">Antal ansatte - 002 - </t>
   </si>
@@ -64,7 +64,13 @@
     <t xml:space="preserve"> Ialt</t>
   </si>
   <si>
-    <t>Aalborg Universitetshospital</t>
+    <t>Aarhus Universitetshospital</t>
+  </si>
+  <si>
+    <t>Odense Universitetshospital</t>
+  </si>
+  <si>
+    <t>Steno Diabetes Center Copenhagen</t>
   </si>
   <si>
     <t>Beskrivelse</t>
@@ -79,7 +85,7 @@
     <t>Datasæt 12 2024</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 14.30.05</t>
+    <t>Kørsel 15.4.2026 14.35.14</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -104,6 +110,15 @@
   </si>
   <si>
     <t>Steno Diabetes Center Nordjylland</t>
+  </si>
+  <si>
+    <t>Steno Diabetes Center Sjælland</t>
+  </si>
+  <si>
+    <t>-Steno Diabetes Center Aarhus</t>
+  </si>
+  <si>
+    <t>-Steno Diabetes Center Odense</t>
   </si>
   <si>
     <t>Ansættelsesform</t>
@@ -588,10 +603,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="14" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -699,40 +714,40 @@
         <v>16</v>
       </c>
       <c r="B4" s="6">
-        <v>745</v>
+        <v>74</v>
       </c>
       <c r="C4" s="6">
-        <v>755</v>
+        <v>74</v>
       </c>
       <c r="D4" s="6">
-        <v>756</v>
+        <v>73</v>
       </c>
       <c r="E4" s="6">
-        <v>748</v>
+        <v>74</v>
       </c>
       <c r="F4" s="6">
-        <v>749</v>
+        <v>76</v>
       </c>
       <c r="G4" s="6">
-        <v>746</v>
+        <v>77</v>
       </c>
       <c r="H4" s="6">
-        <v>744</v>
+        <v>77</v>
       </c>
       <c r="I4" s="6">
-        <v>749</v>
+        <v>77</v>
       </c>
       <c r="J4" s="6">
-        <v>747</v>
+        <v>78</v>
       </c>
       <c r="K4" s="6">
-        <v>743</v>
+        <v>83</v>
       </c>
       <c r="L4" s="6">
-        <v>744</v>
+        <v>83</v>
       </c>
       <c r="M4" s="6">
-        <v>750</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -740,57 +755,129 @@
         <v>17</v>
       </c>
       <c r="B5" s="8">
-        <v>744</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8">
-        <v>754</v>
+        <v>23</v>
       </c>
       <c r="D5" s="8">
-        <v>755</v>
+        <v>23</v>
       </c>
       <c r="E5" s="8">
-        <v>747</v>
+        <v>23</v>
       </c>
       <c r="F5" s="8">
-        <v>748</v>
+        <v>24</v>
       </c>
       <c r="G5" s="8">
-        <v>745</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8">
-        <v>743</v>
+        <v>23</v>
       </c>
       <c r="I5" s="8">
-        <v>748</v>
+        <v>24</v>
       </c>
       <c r="J5" s="8">
-        <v>746</v>
+        <v>24</v>
       </c>
       <c r="K5" s="8">
-        <v>742</v>
+        <v>26</v>
       </c>
       <c r="L5" s="8">
-        <v>743</v>
+        <v>26</v>
       </c>
       <c r="M5" s="8">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="9"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B6" s="6">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6">
+        <v>13</v>
+      </c>
+      <c r="F6" s="6">
+        <v>13</v>
+      </c>
+      <c r="G6" s="6">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6">
+        <v>13</v>
+      </c>
+      <c r="I6" s="6">
+        <v>12</v>
+      </c>
+      <c r="J6" s="6">
+        <v>12</v>
+      </c>
+      <c r="K6" s="6">
+        <v>12</v>
+      </c>
+      <c r="L6" s="6">
+        <v>12</v>
+      </c>
+      <c r="M6" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B7" s="8">
+        <v>36</v>
+      </c>
+      <c r="C7" s="8">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8">
+        <v>35</v>
+      </c>
+      <c r="E7" s="8">
+        <v>37</v>
+      </c>
+      <c r="F7" s="8">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8">
+        <v>38</v>
+      </c>
+      <c r="H7" s="8">
+        <v>39</v>
+      </c>
+      <c r="I7" s="8">
+        <v>39</v>
+      </c>
+      <c r="J7" s="8">
+        <v>40</v>
+      </c>
+      <c r="K7" s="8">
+        <v>43</v>
+      </c>
+      <c r="L7" s="8">
+        <v>43</v>
+      </c>
+      <c r="M7" s="8">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -804,19 +891,21 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
         <v>25</v>
       </c>
     </row>
@@ -828,36 +917,36 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -873,7 +962,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -881,31 +970,31 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -916,34 +1005,66 @@
         <v>39</v>
       </c>
     </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+    </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>42</v>
-      </c>
-    </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
